--- a/AD_Weekly_Load_Tracking_2026-27.xlsx
+++ b/AD_Weekly_Load_Tracking_2026-27.xlsx
@@ -16,10 +16,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -49,9 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -545,9 +541,15 @@
           <t>VBA</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" s="1" t="n">
-        <v>46080</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2026-02-27 00:00:00</t>
+        </is>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -582,9 +584,15 @@
           <t>Python</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" s="1" t="n">
-        <v>46070</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2026-02-17 00:00:00</t>
+        </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -623,14 +631,20 @@
           <t>C#</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" s="1" t="n">
-        <v>46098</v>
-      </c>
-      <c r="I5" s="1" t="n">
-        <v>46112</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2026-03-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2026-03-31 00:00:00</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -664,7 +678,11 @@
           <t>Python</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>WIP</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -699,12 +717,20 @@
           <t>C#</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" s="1" t="n">
-        <v>46119</v>
-      </c>
-      <c r="I7" s="1" t="n">
-        <v>46129</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>WIP</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2026-04-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2026-04-17 00:00:00</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -738,12 +764,20 @@
           <t>VBA</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" s="1" t="n">
-        <v>46127</v>
-      </c>
-      <c r="I8" s="1" t="n">
-        <v>46142</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2026-04-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2026-04-30 00:00:00</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -777,12 +811,20 @@
           <t>VBA</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" s="1" t="n">
-        <v>46139</v>
-      </c>
-      <c r="I9" s="1" t="n">
-        <v>46153</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2026-04-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2026-05-11 00:00:00</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -816,12 +858,20 @@
           <t>VBA</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" s="1" t="n">
-        <v>46136</v>
-      </c>
-      <c r="I10" s="1" t="n">
-        <v>46153</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2026-04-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2026-05-11 00:00:00</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -855,9 +905,15 @@
           <t>Python</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" s="1" t="n">
-        <v>46134</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>WIP</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2026-04-22 00:00:00</t>
+        </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -896,12 +952,20 @@
           <t>Python</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" s="1" t="n">
-        <v>46149</v>
-      </c>
-      <c r="I12" s="1" t="n">
-        <v>46157</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2026-05-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2026-05-15 00:00:00</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -935,94 +999,21 @@
           <t>Python</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" s="1" t="n">
-        <v>46149</v>
-      </c>
-      <c r="I13" s="1" t="n">
-        <v>46157</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>CS713AB</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>COE</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Internal</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>SK</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>CS713BA</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>ADAS-BSW</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Client</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>YS</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>CS753F</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>ADAS</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Internal</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>SR</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>WIP</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2026-05-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2026-05-15 00:00:00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/AD_Weekly_Load_Tracking_2026-27.xlsx
+++ b/AD_Weekly_Load_Tracking_2026-27.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,22 +466,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CS753AC</t>
+          <t>CS753AA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SRMT-xxxxx-Autograph Tool-v1.1</t>
+          <t>TAS_TOOL_VER_2.1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Client</t>
+          <t>In-house</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>SVAT</t>
+          <t>PMO</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -491,7 +491,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>VBA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -501,24 +501,20 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-02-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>2026-02-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CS753AA</t>
+          <t>CS753AB</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>TAS_TOOL_VER_2.1</t>
+          <t>Outlook_Configuration_Tool</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -533,12 +529,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>PS</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>VBA</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -548,20 +544,24 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-02-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>2026-02-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CS753AB</t>
+          <t>CS753AE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Outlook_Configuration_Tool</t>
+          <t>RAM_ROM_Memory_Calculation_Tool</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -571,17 +571,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>PMO</t>
+          <t>SVAT</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>YS</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>C#</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -591,29 +591,29 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-02-17 00:00:00</t>
+          <t>2026-03-17 00:00:00</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-31 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CS753AE</t>
+          <t>CS767G</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>RAM_ROM_Memory_Calculation_Tool</t>
+          <t>NPCU Regression Testing Execution Tool</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>In-house</t>
+          <t>Client</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -623,59 +623,51 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>YS</t>
+          <t>SR, SU</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>C#</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Released</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>2026-03-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2026-03-31 00:00:00</t>
-        </is>
-      </c>
+          <t>WIP</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CS767G</t>
+          <t>CS767H</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NPCU Regression Testing Execution Tool</t>
+          <t>GUNMA_IH_SD_Automation_Tool</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Client</t>
+          <t>In-house</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>SVAT</t>
+          <t>RE-DEV</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>SR, SU</t>
+          <t>YS,PS</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>C#</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -683,18 +675,26 @@
           <t>WIP</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2026-04-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2026-04-17 00:00:00</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CS767H</t>
+          <t>CS767I</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>GUNMA_IH_SD_Automation_Tool</t>
+          <t>GUNMA_IH_CAN FD macro-v1.1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -704,44 +704,44 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>RE-DEV</t>
+          <t>RE-KEN</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>YS,PS</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>C#</t>
+          <t>VBA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>WIP</t>
+          <t>Released</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-04-07 00:00:00</t>
+          <t>2026-04-15 00:00:00</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-04-17 00:00:00</t>
+          <t>2026-04-30 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CS767I</t>
+          <t>CS767J</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>GUNMA_IH_CAN FD macro-v1.1</t>
+          <t>ADAS_IH_SDS_Tool</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -751,12 +751,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>RE-KEN</t>
+          <t>ADAS</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>YS</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -771,24 +771,24 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-04-15 00:00:00</t>
+          <t>2026-04-27 00:00:00</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-04-30 00:00:00</t>
+          <t>2026-05-11 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CS767J</t>
+          <t>CS767K</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ADAS_IH_SDS_Tool</t>
+          <t>MASTA_IH_RAM_Configuration_Support_Tool</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ADAS</t>
+          <t>MASTA</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>YS</t>
+          <t>PS, SG</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-04-27 00:00:00</t>
+          <t>2026-04-24 00:00:00</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -830,74 +830,74 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CS767K</t>
+          <t>-</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>MASTA_IH_RAM_Configuration_Support_Tool</t>
+          <t xml:space="preserve">NEW TOOL Autograph </t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>In-house</t>
+          <t>Client</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>MASTA</t>
+          <t>SVAT</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>PS, SG</t>
+          <t>PS</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>VBA</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Released</t>
+          <t>WIP</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-04-24 00:00:00</t>
+          <t>2026-04-22 00:00:00</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-05-11 00:00:00</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CS767L</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">NEW TOOL Autograph </t>
+          <t>Outlook_Cofiguration_Tool-V1.01</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Client</t>
+          <t>In-House</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>SVAT</t>
+          <t>PMO</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>PS</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -907,29 +907,29 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>WIP</t>
+          <t>Released</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-04-22 00:00:00</t>
+          <t>2026-05-07 00:00:00</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-15 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CS767L</t>
+          <t>CS767N</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Outlook_Cofiguration_Tool-V1.01</t>
+          <t>Status Mail Report Tracking Tool</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Released</t>
+          <t>WIP</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -963,53 +963,6 @@
         </is>
       </c>
       <c r="I12" t="inlineStr">
-        <is>
-          <t>2026-05-15 00:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>CS767N</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Status Mail Report Tracking Tool</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>In-House</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>PMO</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>SG</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>WIP</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>2026-05-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
         <is>
           <t>2026-05-15 00:00:00</t>
         </is>
